--- a/hairdresser_forms/003_reconstructive_keratin_consultation_form--hairdresser_forms.xlsx
+++ b/hairdresser_forms/003_reconstructive_keratin_consultation_form--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>damaged</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Damaged</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hair_condition_choices</t>
+          <t>scalp_condition_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>oily</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oily</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>slightly_dry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Slightly Dry</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>slightly_dry</t>
+          <t>very_dry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slightly Dry</t>
+          <t>Very Dry</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>scalp_condition_choices</t>
+          <t>previous_treatments_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>very_dry</t>
+          <t>keratin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Very Dry</t>
+          <t>Keratin</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>keratin</t>
+          <t>chemical_relaxer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Keratin</t>
+          <t>Chemical Relaxer</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemical_relaxer</t>
+          <t>hair_straightening</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chemical Relaxer</t>
+          <t>Hair Straightening</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hair_straightening</t>
+          <t>hair_smoothing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hair Straightening</t>
+          <t>Hair Smoothing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>previous_treatments_choices</t>
+          <t>hair_goals_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hair_smoothing</t>
+          <t>hair_length</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hair Smoothing</t>
+          <t>Hair Length</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hair_length</t>
+          <t>hair_volume</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hair Length</t>
+          <t>Hair Volume</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hair_volume</t>
+          <t>hair_texture</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hair Volume</t>
+          <t>Hair Texture</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hair_texture</t>
+          <t>hair_color</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hair Texture</t>
+          <t>Hair Color</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hair_color</t>
+          <t>hair_health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hair Color</t>
+          <t>Hair Health</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hair_goals_choices</t>
+          <t>hair_products_used_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hair_health</t>
+          <t>shampoo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hair Health</t>
+          <t>Shampoo</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>shampoo</t>
+          <t>conditioner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shampoo</t>
+          <t>Conditioner</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>conditioner</t>
+          <t>hair_spray</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Hair Spray</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hair_spray</t>
+          <t>hair_serum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hair Spray</t>
+          <t>Hair serum</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hair_products_used_choices</t>
+          <t>hair_products_preferred_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hair_serum</t>
+          <t>shampoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hair serum</t>
+          <t>Shampoo</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>shampoo</t>
+          <t>conditioner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shampoo</t>
+          <t>Conditioner</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>conditioner</t>
+          <t>hair_serum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Hair Serum</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hair_serum</t>
+          <t>hair_mask</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hair Serum</t>
+          <t>Hair Mask</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hair_products_preferred_choices</t>
+          <t>keratin_treatment_goals_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hair_mask</t>
+          <t>to_repair_and_restore</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hair Mask</t>
+          <t>To repair and restore</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>to_repair_and_restore</t>
+          <t>to_smooth_and_straighten</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>To repair and restore</t>
+          <t>To smooth and straighten</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>to_smooth_and_straighten</t>
+          <t>to_strengthen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>To smooth and straighten</t>
+          <t>To strengthen</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>to_strengthen</t>
+          <t>to_add_shine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>To strengthen</t>
+          <t>To add shine</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>keratin_treatment_goals_choices</t>
+          <t>keratin_treatment_concentration_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>to_add_shine</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>To add shine</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>keratin_treatment_concentration_choices</t>
+          <t>hair_color_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>blonde</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Blonde</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>grey</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Grey</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>grey</t>
+          <t>blonde/brown</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>Blonde/Brown</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hair_color_choices</t>
+          <t>chemical_relaxer_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>blonde/brown</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Blonde/Brown</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>between_1-6_months</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>Between 1-6 months</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1896,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>between_1-6_months</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Between 1-6 months</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>chemical_relaxer_choices</t>
+          <t>chemical_removal_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>more_than_6_months</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>More than 6 months</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>between_1-6_months</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>Between 1-6 months</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>between_1-6_months</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Between 1-6 months</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>chemical_removal_choices</t>
+          <t>chemical_processing_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>more_than_6_months</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>More than 6 months</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>between_1-6_months</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>Between 1-6 months</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2032,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>between_1-6_months</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Between 1-6 months</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>chemical_processing_choices</t>
+          <t>chemical_treatment_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>more_than_6_months</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>More than 6 months</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>between_1-6_months</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>Between 1-6 months</t>
         </is>
       </c>
     </row>
@@ -2100,27 +2100,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>between_1-6_months</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>Between 1-6 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>chemical_treatment_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>more_than_6_months</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>More than 6 months</t>
         </is>
